--- a/RDA DMP Common Standard for machine-actionable Data Management Plans.xlsx
+++ b/RDA DMP Common Standard for machine-actionable Data Management Plans.xlsx
@@ -16,11 +16,20 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={2b89195f-16eb-41a0-bd2b-4f77cbcff0e7}</author>
-    <author>tc={34c96070-2e56-4b4f-b08f-f9f9e73d9127}</author>
+    <author>tc={53d81843-f4ec-4dce-a707-4029602e7f91}</author>
+    <author>tc={84785482-26b2-4a4c-b4a6-6ecb01e99164}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{2b89195f-16eb-41a0-bd2b-4f77cbcff0e7}" ref="G76">
+    <comment authorId="0" xr:uid="{53d81843-f4ec-4dce-a707-4029602e7f91}" ref="G152">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	I don’t think the total number really makes sense since each PDF is kind of different, if that makes sense, we can add total as well
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{84785482-26b2-4a4c-b4a6-6ecb01e99164}" ref="G76">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -29,21 +38,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{34c96070-2e56-4b4f-b08f-f9f9e73d9127}" ref="G152">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	I don’t think the total number really makes sense since each PDF is kind of different, if that makes sense, we can add total as well
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2205" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2203" uniqueCount="433">
   <si>
     <t>Order</t>
   </si>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">provenance </t>
   </si>
   <si>
-    <t xml:space="preserve">Please use “smartdmp” for the `provenance` value. This will be used by the DMP Tool internally to keep track of where the DMP came from.
+    <t xml:space="preserve">Please use “dmpbridge” for the `provenance` value. This will be used by the DMP Tool internally to keep track of where the DMP came from.
 </t>
   </si>
   <si>
@@ -1417,12 +1417,6 @@
   </si>
   <si>
     <t>Narrative/template-based DMP content, including sections, questions, and answers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">narrative </t>
-  </si>
-  <si>
-    <t>id</t>
   </si>
   <si>
     <t>Title of the template used to generate or collect the narrative content.</t>
@@ -1740,7 +1734,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Nahid Zeinali" id="{218c3d1a-7e39-45b9-87b1-7ff2dd6769dd}" providerId="google-sheets"/>
+  <x18tc:person displayName="Nahid Zeinali" id="{04d280ea-6bf7-4b4b-b762-e55212c166e5}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -1940,10 +1934,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="G152" dT="2026-04-22T19:17:58.00" personId="{218c3d1a-7e39-45b9-87b1-7ff2dd6769dd}" id="{34c96070-2e56-4b4f-b08f-f9f9e73d9127}" done="0">
+  <x18tc:threadedComment ref="G152" dT="2026-04-22T19:17:58.00" personId="{04d280ea-6bf7-4b4b-b762-e55212c166e5}" id="{53d81843-f4ec-4dce-a707-4029602e7f91}" done="0">
     <x18tc:text xml:space="preserve">I don’t think the total number really makes sense since each PDF is kind of different, if that makes sense, we can add total as well</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="G76" dT="2026-04-23T16:44:25.00" personId="{218c3d1a-7e39-45b9-87b1-7ff2dd6769dd}" id="{2b89195f-16eb-41a0-bd2b-4f77cbcff0e7}" done="0">
+  <x18tc:threadedComment ref="G76" dT="2026-04-23T16:44:25.00" personId="{04d280ea-6bf7-4b4b-b762-e55212c166e5}" id="{84785482-26b2-4a4c-b4a6-6ecb01e99164}" done="0">
     <x18tc:text xml:space="preserve">I added different titles in different colors since the content is nested.</x18tc:text>
   </x18tc:threadedComment>
 </x18tc:ThreadedComments>
@@ -20773,14 +20767,20 @@
         <v>153.0</v>
       </c>
       <c r="B154" s="34" t="s">
+        <v>412</v>
+      </c>
+      <c r="C154" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D154" s="34" t="s">
         <v>414</v>
       </c>
-      <c r="C154" s="34" t="s">
-        <v>415</v>
-      </c>
-      <c r="D154" s="34"/>
-      <c r="E154" s="34"/>
-      <c r="F154" s="37"/>
+      <c r="E154" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="F154" s="37">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="33">
@@ -20790,16 +20790,16 @@
         <v>412</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>44</v>
+        <v>415</v>
       </c>
       <c r="D155" s="34" t="s">
         <v>416</v>
       </c>
       <c r="E155" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="F155" s="37">
-        <v>1.0</v>
+        <v>9</v>
+      </c>
+      <c r="F155" s="37" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="156">
@@ -20807,7 +20807,7 @@
         <v>155.0</v>
       </c>
       <c r="B156" s="34" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C156" s="34" t="s">
         <v>417</v>
@@ -20816,10 +20816,10 @@
         <v>418</v>
       </c>
       <c r="E156" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F156" s="37" t="s">
-        <v>10</v>
+        <v>419</v>
+      </c>
+      <c r="F156" s="37">
+        <v>1.0</v>
       </c>
     </row>
     <row r="157">
@@ -20827,16 +20827,16 @@
         <v>156.0</v>
       </c>
       <c r="B157" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>419</v>
+        <v>44</v>
       </c>
       <c r="D157" s="34" t="s">
         <v>420</v>
       </c>
       <c r="E157" s="34" t="s">
-        <v>421</v>
+        <v>25</v>
       </c>
       <c r="F157" s="37">
         <v>1.0</v>
@@ -20847,19 +20847,19 @@
         <v>157.0</v>
       </c>
       <c r="B158" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C158" s="34" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D158" s="34" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E158" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="F158" s="37">
-        <v>1.0</v>
+      <c r="F158" s="37" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="159">
@@ -20867,19 +20867,19 @@
         <v>158.0</v>
       </c>
       <c r="B159" s="34" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C159" s="34" t="s">
-        <v>23</v>
+        <v>422</v>
       </c>
       <c r="D159" s="34" t="s">
         <v>423</v>
       </c>
       <c r="E159" s="34" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F159" s="37" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160">
@@ -20887,19 +20887,19 @@
         <v>159.0</v>
       </c>
       <c r="B160" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="C160" s="34" t="s">
         <v>417</v>
       </c>
-      <c r="C160" s="34" t="s">
+      <c r="D160" s="34" t="s">
         <v>424</v>
       </c>
-      <c r="D160" s="34" t="s">
-        <v>425</v>
-      </c>
       <c r="E160" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F160" s="37" t="s">
-        <v>10</v>
+        <v>419</v>
+      </c>
+      <c r="F160" s="37">
+        <v>1.0</v>
       </c>
     </row>
     <row r="161">
@@ -20907,16 +20907,16 @@
         <v>160.0</v>
       </c>
       <c r="B161" s="34" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C161" s="34" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D161" s="34" t="s">
         <v>426</v>
       </c>
       <c r="E161" s="34" t="s">
-        <v>421</v>
+        <v>25</v>
       </c>
       <c r="F161" s="37">
         <v>1.0</v>
@@ -20927,7 +20927,7 @@
         <v>161.0</v>
       </c>
       <c r="B162" s="34" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C162" s="34" t="s">
         <v>427</v>
@@ -20936,10 +20936,10 @@
         <v>428</v>
       </c>
       <c r="E162" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="F162" s="37">
-        <v>1.0</v>
+        <v>9</v>
+      </c>
+      <c r="F162" s="37" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="163">
@@ -20947,7 +20947,7 @@
         <v>162.0</v>
       </c>
       <c r="B163" s="34" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C163" s="34" t="s">
         <v>429</v>
@@ -20958,8 +20958,8 @@
       <c r="E163" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="F163" s="37" t="s">
-        <v>26</v>
+      <c r="F163" s="37">
+        <v>1.0</v>
       </c>
     </row>
     <row r="164">
@@ -20970,16 +20970,16 @@
         <v>429</v>
       </c>
       <c r="C164" s="34" t="s">
+        <v>427</v>
+      </c>
+      <c r="D164" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="D164" s="34" t="s">
-        <v>432</v>
-      </c>
       <c r="E164" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164" s="37">
-        <v>1.0</v>
+        <v>25</v>
+      </c>
+      <c r="F164" s="37" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="165">
@@ -20987,40 +20987,24 @@
         <v>164.0</v>
       </c>
       <c r="B165" s="34" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>429</v>
+        <v>56</v>
       </c>
       <c r="D165" s="34" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E165" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="F165" s="37" t="s">
-        <v>26</v>
+      <c r="F165" s="37">
+        <v>1.0</v>
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="33">
-        <v>165.0</v>
-      </c>
-      <c r="B166" s="34" t="s">
-        <v>431</v>
-      </c>
-      <c r="C166" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D166" s="34" t="s">
-        <v>434</v>
-      </c>
-      <c r="E166" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="F166" s="37">
-        <v>1.0</v>
-      </c>
+      <c r="D166" s="38"/>
+      <c r="F166" s="29"/>
     </row>
     <row r="167">
       <c r="D167" s="38"/>
@@ -21043,7 +21027,6 @@
       <c r="F171" s="29"/>
     </row>
     <row r="172">
-      <c r="D172" s="38"/>
       <c r="F172" s="29"/>
     </row>
     <row r="173">
@@ -23529,9 +23512,6 @@
     </row>
     <row r="1000">
       <c r="F1000" s="29"/>
-    </row>
-    <row r="1001">
-      <c r="F1001" s="29"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
